--- a/Assignments/Phase2/Phase2_Week1.xlsx
+++ b/Assignments/Phase2/Phase2_Week1.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyFiles\MyFiles-Learning\GenAI_TestLeaf\HomeWorks\Assignments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyFiles\MyFiles-Learning\GenAI_TestLeaf\Assignments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99413D39-A96E-4E1A-93CD-CFE6172EBC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2CAEBA-9002-43EE-B606-16ACF01778D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="21-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="22-03-2026" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,6 +23,26 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t>API response:</t>
+  </si>
+  <si>
+    <t>Parser</t>
+  </si>
+  <si>
+    <t>GROQ</t>
+  </si>
+  <si>
+    <t>prompt</t>
+  </si>
+  <si>
+    <t>Groq 2</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -156,6 +177,407 @@
         <a:xfrm>
           <a:off x="0" y="7799293"/>
           <a:ext cx="14877016" cy="7903415"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>607314</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>135931</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D5DD863-696E-9110-EB64-E7DF08CD44F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="10058400"/>
+          <a:ext cx="18285714" cy="9828571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>607314</xdr:colOff>
+      <xdr:row>164</xdr:row>
+      <xdr:rowOff>135931</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C3780BA-A25A-C350-D3BD-FC17587B9856}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="20299680"/>
+          <a:ext cx="18285714" cy="9828571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>607314</xdr:colOff>
+      <xdr:row>221</xdr:row>
+      <xdr:rowOff>135931</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{091C40BE-0460-15D6-B64B-A03C30AF96C5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="30723840"/>
+          <a:ext cx="18285714" cy="9828571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>225</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>607314</xdr:colOff>
+      <xdr:row>278</xdr:row>
+      <xdr:rowOff>135931</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB1A879E-66B3-8D18-72AE-D6766B4332B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="41148000"/>
+          <a:ext cx="18285714" cy="9828571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>42531</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{563F1450-A027-4BF0-9B80-08F8EA984D3C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="14672931" cy="7886700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>282</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>607314</xdr:colOff>
+      <xdr:row>335</xdr:row>
+      <xdr:rowOff>135931</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5455E69-54C5-70CC-0DCE-5F5BBA5E923A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="51572160"/>
+          <a:ext cx="18285714" cy="9828571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>338</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>607314</xdr:colOff>
+      <xdr:row>391</xdr:row>
+      <xdr:rowOff>135931</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C23234CA-67A7-CC77-B865-F58AD56E2BD5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="61813440"/>
+          <a:ext cx="18285714" cy="9828571"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>396</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>607314</xdr:colOff>
+      <xdr:row>449</xdr:row>
+      <xdr:rowOff>21646</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63EEEB74-6251-F3AD-F331-A5CC303D8FA1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="72420480"/>
+          <a:ext cx="18285714" cy="9714286"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>452</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>607314</xdr:colOff>
+      <xdr:row>505</xdr:row>
+      <xdr:rowOff>21646</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0689BDDB-31BD-2B2A-E3AD-8DCB7F626BBB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="82661760"/>
+          <a:ext cx="18285714" cy="9714286"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -436,4 +858,40 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1A1AEB3-BBF1-44D2-8B6A-2B82721F0AC2}">
+  <dimension ref="A55:A282"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>